--- a/diseases/d065/2010-2014.xlsx
+++ b/diseases/d065/2010-2014.xlsx
@@ -53874,6 +53874,11 @@
       <c r="R392" t="n">
         <v>0</v>
       </c>
+      <c r="S392" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U392" t="inlineStr">
         <is>
           <t>HOLD_CH_b72471754ba1860d0eddb1a769dc</t>
@@ -53891,7 +53896,12 @@
       </c>
       <c r="AP392" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ392" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS392" t="inlineStr">
@@ -53901,6 +53911,11 @@
       </c>
       <c r="AT392" t="n">
         <v>1</v>
+      </c>
+      <c r="AU392" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
       </c>
       <c r="AV392" t="inlineStr">
         <is>
@@ -71316,6 +71331,11 @@
       <c r="R520" t="n">
         <v>0</v>
       </c>
+      <c r="S520" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U520" t="inlineStr">
         <is>
           <t>HOLD_CH_b72471754ba1860d0eddb1a769dc</t>
@@ -71333,7 +71353,12 @@
       </c>
       <c r="AP520" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ520" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS520" t="inlineStr">
@@ -71343,6 +71368,11 @@
       </c>
       <c r="AT520" t="n">
         <v>1</v>
+      </c>
+      <c r="AU520" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
       </c>
       <c r="AV520" t="inlineStr">
         <is>
